--- a/src/src/main/webapp/portal/asset/assetImport/APM_Asset_Template.xlsx
+++ b/src/src/main/webapp/portal/asset/assetImport/APM_Asset_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\212670825\Desktop\APM\Git\hc-apm-web\src\src\main\webapp\portal\asset\assetImport\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:100000_{56B613D4-0797-45E2-9744-CA4DE829B4DA}" xr6:coauthVersionLast="31" xr6:coauthVersionMax="31" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:100000_{23983298-9667-4ACA-B345-158FC6A8DC2F}" xr6:coauthVersionLast="31" xr6:coauthVersionMax="31" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="465" windowWidth="29040" windowHeight="18240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -84,7 +84,7 @@
     <definedName name="计量等级">设备分类!$F$2:$F$6</definedName>
     <definedName name="计量项目类别">设备分类!$I$2:$I$36</definedName>
     <definedName name="计量状态">设备分类!$K$2:$K$5</definedName>
-    <definedName name="设备分类">设备分类!$A$2:$A$14</definedName>
+    <definedName name="设备分类">设备分类!$B$2:$B$14</definedName>
     <definedName name="是否">设备分类!$N$2:$N$3</definedName>
     <definedName name="是否急救设备">设备分类!$G$2:$G$4</definedName>
     <definedName name="是否进口设备">设备分类!$H$2:$H$4</definedName>
@@ -3806,19 +3806,7 @@
     <cellStyle name="Total counts" xfId="14" xr:uid="{00000000-0005-0000-0000-00000E000000}"/>
     <cellStyle name="常规 2" xfId="15" xr:uid="{00000000-0005-0000-0000-00000F000000}"/>
   </cellStyles>
-  <dxfs count="42">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
+  <dxfs count="40">
     <dxf>
       <font>
         <b/>
@@ -4082,14 +4070,14 @@
   </dxfs>
   <tableStyles count="2" defaultTableStyle="Warehouse Inventory" defaultPivotStyle="PivotStyleMedium2">
     <tableStyle name="MySqlDefault" pivot="0" table="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" dxfId="41"/>
-      <tableStyleElement type="headerRow" dxfId="40"/>
+      <tableStyleElement type="wholeTable" dxfId="39"/>
+      <tableStyleElement type="headerRow" dxfId="38"/>
     </tableStyle>
     <tableStyle name="Warehouse Inventory" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
-      <tableStyleElement type="wholeTable" dxfId="39"/>
-      <tableStyleElement type="headerRow" dxfId="38"/>
-      <tableStyleElement type="lastColumn" dxfId="37"/>
-      <tableStyleElement type="secondRowStripe" dxfId="36"/>
+      <tableStyleElement type="wholeTable" dxfId="37"/>
+      <tableStyleElement type="headerRow" dxfId="36"/>
+      <tableStyleElement type="lastColumn" dxfId="35"/>
+      <tableStyleElement type="secondRowStripe" dxfId="34"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -63379,17 +63367,17 @@
   <autoFilter ref="A6:BF6" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="18" type="noConversion"/>
   <conditionalFormatting sqref="D1 E4:H5 R7:T7 AB501 E501:H5029 E6:G6 B7:M500 BG7:BG500">
-    <cfRule type="expression" dxfId="35" priority="85">
+    <cfRule type="expression" dxfId="33" priority="85">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2">
-    <cfRule type="expression" dxfId="34" priority="58">
+    <cfRule type="expression" dxfId="32" priority="58">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U7:AK7 N7:O7">
-    <cfRule type="expression" dxfId="33" priority="56">
+    <cfRule type="expression" dxfId="31" priority="56">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -63408,7 +63396,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF7">
-    <cfRule type="expression" dxfId="32" priority="54">
+    <cfRule type="expression" dxfId="30" priority="54">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -63427,12 +63415,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AN7:AP7">
-    <cfRule type="expression" dxfId="31" priority="40">
+    <cfRule type="expression" dxfId="29" priority="40">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AG7">
-    <cfRule type="expression" dxfId="30" priority="52">
+    <cfRule type="expression" dxfId="28" priority="52">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -63451,7 +63439,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH7:AI7">
-    <cfRule type="expression" dxfId="29" priority="50">
+    <cfRule type="expression" dxfId="27" priority="50">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -63470,7 +63458,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AJ7">
-    <cfRule type="expression" dxfId="28" priority="48">
+    <cfRule type="expression" dxfId="26" priority="48">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -63489,7 +63477,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AK7">
-    <cfRule type="expression" dxfId="27" priority="46">
+    <cfRule type="expression" dxfId="25" priority="46">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -63508,7 +63496,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AL7">
-    <cfRule type="expression" dxfId="26" priority="44">
+    <cfRule type="expression" dxfId="24" priority="44">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -63527,7 +63515,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AM7">
-    <cfRule type="expression" dxfId="25" priority="42">
+    <cfRule type="expression" dxfId="23" priority="42">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -63560,77 +63548,77 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2">
-    <cfRule type="expression" dxfId="24" priority="37">
+    <cfRule type="expression" dxfId="22" priority="37">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P7:Q7">
-    <cfRule type="expression" dxfId="23" priority="35">
+    <cfRule type="expression" dxfId="21" priority="35">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A7">
-    <cfRule type="expression" dxfId="22" priority="31">
+    <cfRule type="expression" dxfId="20" priority="31">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A8:A500">
-    <cfRule type="expression" dxfId="21" priority="8">
+    <cfRule type="expression" dxfId="19" priority="8">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R8:T500">
-    <cfRule type="expression" dxfId="20" priority="29">
+    <cfRule type="expression" dxfId="18" priority="29">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U8:AK500 N8:O500">
-    <cfRule type="expression" dxfId="19" priority="27">
+    <cfRule type="expression" dxfId="17" priority="27">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF8:AF500">
-    <cfRule type="expression" dxfId="18" priority="25">
+    <cfRule type="expression" dxfId="16" priority="25">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AN8:AP500">
-    <cfRule type="expression" dxfId="17" priority="11">
+    <cfRule type="expression" dxfId="15" priority="11">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AG8:AG500">
-    <cfRule type="expression" dxfId="16" priority="23">
+    <cfRule type="expression" dxfId="14" priority="23">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH8:AI500">
-    <cfRule type="expression" dxfId="15" priority="21">
+    <cfRule type="expression" dxfId="13" priority="21">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AJ8:AJ500">
-    <cfRule type="expression" dxfId="14" priority="19">
+    <cfRule type="expression" dxfId="12" priority="19">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AK8:AK500">
-    <cfRule type="expression" dxfId="13" priority="17">
+    <cfRule type="expression" dxfId="11" priority="17">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AL8:AL500">
-    <cfRule type="expression" dxfId="12" priority="15">
+    <cfRule type="expression" dxfId="10" priority="15">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AM8:AM500">
-    <cfRule type="expression" dxfId="11" priority="13">
+    <cfRule type="expression" dxfId="9" priority="13">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P8:Q500">
-    <cfRule type="expression" dxfId="10" priority="10">
+    <cfRule type="expression" dxfId="8" priority="10">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -63775,32 +63763,32 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BI7:BI8">
-    <cfRule type="expression" dxfId="9" priority="7">
+    <cfRule type="expression" dxfId="7" priority="7">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BH7">
-    <cfRule type="expression" dxfId="8" priority="6">
+    <cfRule type="expression" dxfId="6" priority="6">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BH8">
-    <cfRule type="expression" dxfId="7" priority="5">
+    <cfRule type="expression" dxfId="5" priority="5">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BH9 BH11 BH13 BH15 BH17 BH19 BH21 BH23 BH25 BH27 BH29 BH31 BH33 BH35 BH37 BH39 BH41 BH43 BH45 BH47 BH49 BH51 BH53 BH55 BH57 BH59 BH61 BH63 BH65 BH67 BH69 BH71 BH73 BH75 BH77 BH79 BH81 BH83 BH85 BH87 BH89 BH91 BH93 BH95 BH97 BH99 BH101 BH103 BH105 BH107 BH109 BH111 BH113 BH115 BH117 BH119 BH121 BH123 BH125 BH127 BH129 BH131 BH133 BH135 BH137 BH139 BH141 BH143 BH145 BH147 BH149 BH151 BH153 BH155 BH157 BH159 BH161 BH163 BH165 BH167 BH169 BH171 BH173 BH175 BH177 BH179 BH181 BH183 BH185 BH187 BH189 BH191 BH193 BH195 BH197 BH199 BH201 BH203 BH205 BH207 BH209 BH211 BH213 BH215 BH217 BH219 BH221 BH223 BH225 BH227 BH229 BH231 BH233 BH235 BH237 BH239 BH241 BH243 BH245 BH247 BH249 BH251 BH253 BH255 BH257 BH259 BH261 BH263 BH265 BH267 BH269 BH271 BH273 BH275 BH277 BH279 BH281 BH283 BH285 BH287 BH289 BH291 BH293 BH295 BH297 BH299 BH301 BH303 BH305 BH307 BH309 BH311 BH313 BH315 BH317 BH319 BH321 BH323 BH325 BH327 BH329 BH331 BH333 BH335 BH337 BH339 BH341 BH343 BH345 BH347 BH349 BH351 BH353 BH355 BH357 BH359 BH361 BH363 BH365 BH367 BH369 BH371 BH373 BH375 BH377 BH379 BH381 BH383 BH385 BH387 BH389 BH391 BH393 BH395 BH397 BH399 BH401 BH403 BH405 BH407 BH409 BH411 BH413 BH415 BH417 BH419 BH421 BH423 BH425 BH427 BH429 BH431 BH433 BH435 BH437 BH439 BH441 BH443 BH445 BH447 BH449 BH451 BH453 BH455 BH457 BH459 BH461 BH463 BH465 BH467 BH469 BH471 BH473 BH475 BH477 BH479 BH481 BH483 BH485 BH487 BH489 BH491 BH493 BH495 BH497 BH499">
-    <cfRule type="expression" dxfId="6" priority="3">
+    <cfRule type="expression" dxfId="4" priority="3">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BH10 BH12 BH14 BH16 BH18 BH20 BH22 BH24 BH26 BH28 BH30 BH32 BH34 BH36 BH38 BH40 BH42 BH44 BH46 BH48 BH50 BH52 BH54 BH56 BH58 BH60 BH62 BH64 BH66 BH68 BH70 BH72 BH74 BH76 BH78 BH80 BH82 BH84 BH86 BH88 BH90 BH92 BH94 BH96 BH98 BH100 BH102 BH104 BH106 BH108 BH110 BH112 BH114 BH116 BH118 BH120 BH122 BH124 BH126 BH128 BH130 BH132 BH134 BH136 BH138 BH140 BH142 BH144 BH146 BH148 BH150 BH152 BH154 BH156 BH158 BH160 BH162 BH164 BH166 BH168 BH170 BH172 BH174 BH176 BH178 BH180 BH182 BH184 BH186 BH188 BH190 BH192 BH194 BH196 BH198 BH200 BH202 BH204 BH206 BH208 BH210 BH212 BH214 BH216 BH218 BH220 BH222 BH224 BH226 BH228 BH230 BH232 BH234 BH236 BH238 BH240 BH242 BH244 BH246 BH248 BH250 BH252 BH254 BH256 BH258 BH260 BH262 BH264 BH266 BH268 BH270 BH272 BH274 BH276 BH278 BH280 BH282 BH284 BH286 BH288 BH290 BH292 BH294 BH296 BH298 BH300 BH302 BH304 BH306 BH308 BH310 BH312 BH314 BH316 BH318 BH320 BH322 BH324 BH326 BH328 BH330 BH332 BH334 BH336 BH338 BH340 BH342 BH344 BH346 BH348 BH350 BH352 BH354 BH356 BH358 BH360 BH362 BH364 BH366 BH368 BH370 BH372 BH374 BH376 BH378 BH380 BH382 BH384 BH386 BH388 BH390 BH392 BH394 BH396 BH398 BH400 BH402 BH404 BH406 BH408 BH410 BH412 BH414 BH416 BH418 BH420 BH422 BH424 BH426 BH428 BH430 BH432 BH434 BH436 BH438 BH440 BH442 BH444 BH446 BH448 BH450 BH452 BH454 BH456 BH458 BH460 BH462 BH464 BH466 BH468 BH470 BH472 BH474 BH476 BH478 BH480 BH482 BH484 BH486 BH488 BH490 BH492 BH494 BH496 BH498 BH500">
-    <cfRule type="expression" dxfId="4" priority="2">
+    <cfRule type="expression" dxfId="3" priority="2">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BI9:BI500">
-    <cfRule type="expression" dxfId="3" priority="1">
+    <cfRule type="expression" dxfId="2" priority="1">
       <formula>"If(blnBinNo=""True"")"</formula>
     </cfRule>
   </conditionalFormatting>
